--- a/src/Accounting.Web/Templates/SubjectDataTemplate.xlsx
+++ b/src/Accounting.Web/Templates/SubjectDataTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22871" windowHeight="8580"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="183">
   <si>
     <t>Code</t>
   </si>
@@ -40,7 +40,7 @@
     <t>OtherName</t>
   </si>
   <si>
-    <t>SubjectCategoryCode</t>
+    <t>SubjectCategory</t>
   </si>
   <si>
     <t>IsSubSubjectType</t>
@@ -49,10 +49,10 @@
     <t>DebitorCreditor</t>
   </si>
   <si>
-    <t>CurrencyCode</t>
-  </si>
-  <si>
-    <t>AccountTypeCode</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>AccountType</t>
   </si>
   <si>
     <t>Description</t>
@@ -64,7 +64,7 @@
     <t>IsPayMethod</t>
   </si>
   <si>
-    <t>SeqCode</t>
+    <t>Seq</t>
   </si>
   <si>
     <t>臨時／暫存帳戶</t>
@@ -73,6 +73,9 @@
     <t>Suspense Account</t>
   </si>
   <si>
+    <t>CR</t>
+  </si>
+  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
   </si>
   <si>
     <t>Furniture &amp; Fixtures (Org. Value)</t>
+  </si>
+  <si>
+    <t>DR</t>
   </si>
   <si>
     <t>FA</t>
@@ -1564,14 +1570,14 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>-1</v>
+      <c r="F2" t="s">
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1588,10 +1594,10 @@
         <v>1111</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>111</v>
@@ -1599,14 +1605,14 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="F3" t="s">
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1623,10 +1629,10 @@
         <v>1112</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>111</v>
@@ -1634,14 +1640,14 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" t="s">
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1658,10 +1664,10 @@
         <v>1121</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>112</v>
@@ -1669,14 +1675,14 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="F5" t="s">
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1693,10 +1699,10 @@
         <v>1122</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>112</v>
@@ -1704,14 +1710,14 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>1</v>
+      <c r="F6" t="s">
+        <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1728,10 +1734,10 @@
         <v>1131</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>113</v>
@@ -1739,14 +1745,14 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="s">
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1763,10 +1769,10 @@
         <v>1132</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>113</v>
@@ -1774,14 +1780,14 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="s">
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1798,10 +1804,10 @@
         <v>1141</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>114</v>
@@ -1809,14 +1815,14 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>1</v>
+      <c r="F9" t="s">
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1833,10 +1839,10 @@
         <v>1142</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>114</v>
@@ -1844,14 +1850,14 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="s">
+        <v>19</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1868,10 +1874,10 @@
         <v>1151</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>115</v>
@@ -1879,14 +1885,14 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="F11" t="s">
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1903,10 +1909,10 @@
         <v>1152</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12">
         <v>115</v>
@@ -1914,14 +1920,14 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="F12" t="s">
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1938,10 +1944,10 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1949,14 +1955,14 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="F13" t="s">
+        <v>19</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1973,10 +1979,10 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -1984,14 +1990,14 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14">
-        <v>1</v>
+      <c r="F14" t="s">
+        <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2008,10 +2014,10 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2019,14 +2025,14 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15">
-        <v>1</v>
+      <c r="F15" t="s">
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2043,10 +2049,10 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2054,14 +2060,14 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" t="s">
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2078,10 +2084,10 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2089,14 +2095,14 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>1</v>
+      <c r="F17" t="s">
+        <v>19</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2113,10 +2119,10 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2124,14 +2130,14 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>1</v>
+      <c r="F18" t="s">
+        <v>19</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2148,10 +2154,10 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2159,14 +2165,14 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>1</v>
+      <c r="F19" t="s">
+        <v>19</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2183,10 +2189,10 @@
         <v>2801</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20">
         <v>28</v>
@@ -2194,14 +2200,14 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>1</v>
+      <c r="F20" t="s">
+        <v>19</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2218,10 +2224,10 @@
         <v>2802</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D21">
         <v>28</v>
@@ -2229,14 +2235,14 @@
       <c r="E21">
         <v>0</v>
       </c>
-      <c r="F21">
-        <v>1</v>
+      <c r="F21" t="s">
+        <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2253,10 +2259,10 @@
         <v>2803</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D22">
         <v>28</v>
@@ -2264,14 +2270,14 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22">
-        <v>1</v>
+      <c r="F22" t="s">
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2288,10 +2294,10 @@
         <v>2804</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23">
         <v>28</v>
@@ -2299,14 +2305,14 @@
       <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23">
-        <v>1</v>
+      <c r="F23" t="s">
+        <v>19</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2323,10 +2329,10 @@
         <v>2805</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D24">
         <v>28</v>
@@ -2334,14 +2340,14 @@
       <c r="E24">
         <v>0</v>
       </c>
-      <c r="F24">
-        <v>1</v>
+      <c r="F24" t="s">
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2358,10 +2364,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -2369,14 +2375,14 @@
       <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25">
-        <v>1</v>
+      <c r="F25" t="s">
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2393,10 +2399,10 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -2404,14 +2410,14 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>-1</v>
+      <c r="F26" t="s">
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2428,10 +2434,10 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -2439,14 +2445,14 @@
       <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27">
-        <v>-1</v>
+      <c r="F27" t="s">
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2463,10 +2469,10 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D28">
         <v>4</v>
@@ -2474,14 +2480,14 @@
       <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28">
-        <v>-1</v>
+      <c r="F28" t="s">
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2498,10 +2504,10 @@
         <v>461</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D29">
         <v>46</v>
@@ -2509,14 +2515,14 @@
       <c r="E29">
         <v>0</v>
       </c>
-      <c r="F29">
-        <v>-1</v>
+      <c r="F29" t="s">
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2533,10 +2539,10 @@
         <v>462</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D30">
         <v>46</v>
@@ -2544,14 +2550,14 @@
       <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30">
-        <v>-1</v>
+      <c r="F30" t="s">
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2568,10 +2574,10 @@
         <v>47</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -2579,14 +2585,14 @@
       <c r="E31">
         <v>0</v>
       </c>
-      <c r="F31">
-        <v>-1</v>
+      <c r="F31" t="s">
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2603,10 +2609,10 @@
         <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -2614,14 +2620,14 @@
       <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32">
-        <v>-1</v>
+      <c r="F32" t="s">
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2638,10 +2644,10 @@
         <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -2649,14 +2655,14 @@
       <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33">
-        <v>-1</v>
+      <c r="F33" t="s">
+        <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2673,10 +2679,10 @@
         <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -2684,14 +2690,14 @@
       <c r="E34">
         <v>0</v>
       </c>
-      <c r="F34">
-        <v>-1</v>
+      <c r="F34" t="s">
+        <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2708,10 +2714,10 @@
         <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -2719,14 +2725,14 @@
       <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35">
-        <v>-1</v>
+      <c r="F35" t="s">
+        <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2743,10 +2749,10 @@
         <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -2754,14 +2760,14 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36">
-        <v>-1</v>
+      <c r="F36" t="s">
+        <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2778,10 +2784,10 @@
         <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D37">
         <v>5</v>
@@ -2789,14 +2795,14 @@
       <c r="E37">
         <v>0</v>
       </c>
-      <c r="F37">
-        <v>-1</v>
+      <c r="F37" t="s">
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2813,10 +2819,10 @@
         <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -2824,14 +2830,14 @@
       <c r="E38">
         <v>0</v>
       </c>
-      <c r="F38">
-        <v>-1</v>
+      <c r="F38" t="s">
+        <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2848,10 +2854,10 @@
         <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D39">
         <v>6</v>
@@ -2859,14 +2865,14 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39">
-        <v>-1</v>
+      <c r="F39" t="s">
+        <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2883,10 +2889,10 @@
         <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D40">
         <v>6</v>
@@ -2894,14 +2900,14 @@
       <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40">
-        <v>-1</v>
+      <c r="F40" t="s">
+        <v>14</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2918,10 +2924,10 @@
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -2929,14 +2935,14 @@
       <c r="E41">
         <v>0</v>
       </c>
-      <c r="F41">
-        <v>-1</v>
+      <c r="F41" t="s">
+        <v>14</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2953,10 +2959,10 @@
         <v>65</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D42">
         <v>6</v>
@@ -2964,14 +2970,14 @@
       <c r="E42">
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>-1</v>
+      <c r="F42" t="s">
+        <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2988,10 +2994,10 @@
         <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D43">
         <v>6</v>
@@ -2999,14 +3005,14 @@
       <c r="E43">
         <v>0</v>
       </c>
-      <c r="F43">
-        <v>-1</v>
+      <c r="F43" t="s">
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3023,10 +3029,10 @@
         <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D44">
         <v>6</v>
@@ -3034,14 +3040,14 @@
       <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44">
-        <v>-1</v>
+      <c r="F44" t="s">
+        <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -3058,10 +3064,10 @@
         <v>68</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D45">
         <v>6</v>
@@ -3069,14 +3075,14 @@
       <c r="E45">
         <v>0</v>
       </c>
-      <c r="F45">
-        <v>-1</v>
+      <c r="F45" t="s">
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -3093,10 +3099,10 @@
         <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D46">
         <v>6</v>
@@ -3104,14 +3110,14 @@
       <c r="E46">
         <v>0</v>
       </c>
-      <c r="F46">
-        <v>-1</v>
+      <c r="F46" t="s">
+        <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -3128,10 +3134,10 @@
         <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D47">
         <v>7</v>
@@ -3139,14 +3145,14 @@
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="F47">
-        <v>1</v>
+      <c r="F47" t="s">
+        <v>19</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -3163,10 +3169,10 @@
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D48">
         <v>7</v>
@@ -3174,14 +3180,14 @@
       <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48">
-        <v>1</v>
+      <c r="F48" t="s">
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -3198,10 +3204,10 @@
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -3209,14 +3215,14 @@
       <c r="E49">
         <v>0</v>
       </c>
-      <c r="F49">
-        <v>1</v>
+      <c r="F49" t="s">
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -3233,10 +3239,10 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D50">
         <v>7</v>
@@ -3244,14 +3250,14 @@
       <c r="E50">
         <v>0</v>
       </c>
-      <c r="F50">
-        <v>1</v>
+      <c r="F50" t="s">
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -3268,10 +3274,10 @@
         <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D51">
         <v>7</v>
@@ -3279,14 +3285,14 @@
       <c r="E51">
         <v>0</v>
       </c>
-      <c r="F51">
-        <v>1</v>
+      <c r="F51" t="s">
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -3303,10 +3309,10 @@
         <v>8011</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D52">
         <v>801</v>
@@ -3314,14 +3320,14 @@
       <c r="E52">
         <v>0</v>
       </c>
-      <c r="F52">
-        <v>1</v>
+      <c r="F52" t="s">
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -3338,10 +3344,10 @@
         <v>8012</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D53">
         <v>801</v>
@@ -3349,14 +3355,14 @@
       <c r="E53">
         <v>0</v>
       </c>
-      <c r="F53">
-        <v>1</v>
+      <c r="F53" t="s">
+        <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -3373,10 +3379,10 @@
         <v>8021</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D54">
         <v>802</v>
@@ -3384,14 +3390,14 @@
       <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54">
-        <v>1</v>
+      <c r="F54" t="s">
+        <v>19</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -3408,10 +3414,10 @@
         <v>8022</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D55">
         <v>802</v>
@@ -3419,14 +3425,14 @@
       <c r="E55">
         <v>0</v>
       </c>
-      <c r="F55">
-        <v>1</v>
+      <c r="F55" t="s">
+        <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -3443,10 +3449,10 @@
         <v>8023</v>
       </c>
       <c r="B56" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D56">
         <v>802</v>
@@ -3454,14 +3460,14 @@
       <c r="E56">
         <v>0</v>
       </c>
-      <c r="F56">
-        <v>1</v>
+      <c r="F56" t="s">
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -3478,10 +3484,10 @@
         <v>8024</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D57">
         <v>802</v>
@@ -3489,14 +3495,14 @@
       <c r="E57">
         <v>0</v>
       </c>
-      <c r="F57">
-        <v>1</v>
+      <c r="F57" t="s">
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -3513,10 +3519,10 @@
         <v>8031</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D58">
         <v>803</v>
@@ -3524,14 +3530,14 @@
       <c r="E58">
         <v>0</v>
       </c>
-      <c r="F58">
-        <v>1</v>
+      <c r="F58" t="s">
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -3548,10 +3554,10 @@
         <v>8032</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D59">
         <v>803</v>
@@ -3559,14 +3565,14 @@
       <c r="E59">
         <v>0</v>
       </c>
-      <c r="F59">
-        <v>1</v>
+      <c r="F59" t="s">
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3583,10 +3589,10 @@
         <v>8033</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C60" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D60">
         <v>803</v>
@@ -3594,14 +3600,14 @@
       <c r="E60">
         <v>0</v>
       </c>
-      <c r="F60">
-        <v>1</v>
+      <c r="F60" t="s">
+        <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H60" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J60">
         <v>1</v>
@@ -3618,10 +3624,10 @@
         <v>8041</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D61">
         <v>804</v>
@@ -3629,14 +3635,14 @@
       <c r="E61">
         <v>0</v>
       </c>
-      <c r="F61">
-        <v>1</v>
+      <c r="F61" t="s">
+        <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -3653,10 +3659,10 @@
         <v>8042</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C62" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D62">
         <v>804</v>
@@ -3664,14 +3670,14 @@
       <c r="E62">
         <v>0</v>
       </c>
-      <c r="F62">
-        <v>1</v>
+      <c r="F62" t="s">
+        <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H62" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -3688,10 +3694,10 @@
         <v>8043</v>
       </c>
       <c r="B63" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D63">
         <v>804</v>
@@ -3699,14 +3705,14 @@
       <c r="E63">
         <v>0</v>
       </c>
-      <c r="F63">
-        <v>1</v>
+      <c r="F63" t="s">
+        <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -3723,10 +3729,10 @@
         <v>8044</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D64">
         <v>804</v>
@@ -3734,14 +3740,14 @@
       <c r="E64">
         <v>0</v>
       </c>
-      <c r="F64">
-        <v>1</v>
+      <c r="F64" t="s">
+        <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3758,10 +3764,10 @@
         <v>8051</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D65">
         <v>805</v>
@@ -3769,14 +3775,14 @@
       <c r="E65">
         <v>0</v>
       </c>
-      <c r="F65">
-        <v>1</v>
+      <c r="F65" t="s">
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -3793,10 +3799,10 @@
         <v>8052</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D66">
         <v>805</v>
@@ -3804,14 +3810,14 @@
       <c r="E66">
         <v>0</v>
       </c>
-      <c r="F66">
-        <v>1</v>
+      <c r="F66" t="s">
+        <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -3828,10 +3834,10 @@
         <v>8053</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D67">
         <v>805</v>
@@ -3839,14 +3845,14 @@
       <c r="E67">
         <v>0</v>
       </c>
-      <c r="F67">
-        <v>1</v>
+      <c r="F67" t="s">
+        <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3863,10 +3869,10 @@
         <v>8054</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D68">
         <v>805</v>
@@ -3874,14 +3880,14 @@
       <c r="E68">
         <v>0</v>
       </c>
-      <c r="F68">
-        <v>1</v>
+      <c r="F68" t="s">
+        <v>19</v>
       </c>
       <c r="G68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3898,10 +3904,10 @@
         <v>8061</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C69" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D69">
         <v>806</v>
@@ -3909,14 +3915,14 @@
       <c r="E69">
         <v>0</v>
       </c>
-      <c r="F69">
-        <v>1</v>
+      <c r="F69" t="s">
+        <v>19</v>
       </c>
       <c r="G69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3933,10 +3939,10 @@
         <v>8071</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D70">
         <v>807</v>
@@ -3944,14 +3950,14 @@
       <c r="E70">
         <v>0</v>
       </c>
-      <c r="F70">
-        <v>1</v>
+      <c r="F70" t="s">
+        <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3968,10 +3974,10 @@
         <v>808</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D71">
         <v>8</v>
@@ -3979,14 +3985,14 @@
       <c r="E71">
         <v>0</v>
       </c>
-      <c r="F71">
-        <v>1</v>
+      <c r="F71" t="s">
+        <v>19</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H71" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -4003,10 +4009,10 @@
         <v>809</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D72">
         <v>8</v>
@@ -4014,14 +4020,14 @@
       <c r="E72">
         <v>0</v>
       </c>
-      <c r="F72">
-        <v>1</v>
+      <c r="F72" t="s">
+        <v>19</v>
       </c>
       <c r="G72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -4038,10 +4044,10 @@
         <v>810</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D73">
         <v>8</v>
@@ -4049,14 +4055,14 @@
       <c r="E73">
         <v>0</v>
       </c>
-      <c r="F73">
-        <v>1</v>
+      <c r="F73" t="s">
+        <v>19</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H73" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -4073,10 +4079,10 @@
         <v>811</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D74">
         <v>8</v>
@@ -4084,14 +4090,14 @@
       <c r="E74">
         <v>0</v>
       </c>
-      <c r="F74">
-        <v>1</v>
+      <c r="F74" t="s">
+        <v>19</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -4108,10 +4114,10 @@
         <v>91</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C75" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D75">
         <v>9</v>
@@ -4119,14 +4125,14 @@
       <c r="E75">
         <v>0</v>
       </c>
-      <c r="F75">
-        <v>1</v>
+      <c r="F75" t="s">
+        <v>19</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -4143,10 +4149,10 @@
         <v>92</v>
       </c>
       <c r="B76" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C76" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D76">
         <v>9</v>
@@ -4154,14 +4160,14 @@
       <c r="E76">
         <v>0</v>
       </c>
-      <c r="F76">
-        <v>1</v>
+      <c r="F76" t="s">
+        <v>19</v>
       </c>
       <c r="G76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H76" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -4178,10 +4184,10 @@
         <v>93</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C77" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D77">
         <v>9</v>
@@ -4189,14 +4195,14 @@
       <c r="E77">
         <v>0</v>
       </c>
-      <c r="F77">
-        <v>1</v>
+      <c r="F77" t="s">
+        <v>19</v>
       </c>
       <c r="G77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -4209,6 +4215,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576 J2:J1048576 K2:K1048576">
+      <formula1>"1,0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F13 F14:F25 F26:F46 F47:F77 F78:F1048576">
+      <formula1>"DR,CR"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
